--- a/data/trans_dic/P40_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P40_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,66; 87,41</t>
+          <t>78,7; 87,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,76; 82,45</t>
+          <t>72,7; 82,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,58; 79,74</t>
+          <t>69,91; 80,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,64; 79,68</t>
+          <t>70,57; 80,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,73; 84,06</t>
+          <t>73,42; 83,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,56; 66,81</t>
+          <t>54,32; 66,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,55; 71,32</t>
+          <t>60,25; 71,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,2; 71,05</t>
+          <t>62,65; 70,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,18; 84,65</t>
+          <t>78,11; 84,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,14; 73,1</t>
+          <t>65,42; 73,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66,75; 74,26</t>
+          <t>66,47; 74,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,75; 74,64</t>
+          <t>67,86; 73,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,16; 87,65</t>
+          <t>81,51; 88,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,08; 87,15</t>
+          <t>80,41; 87,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,04; 90,92</t>
+          <t>84,83; 90,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,49; 87,2</t>
+          <t>79,94; 87,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,46; 75,09</t>
+          <t>67,33; 75,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,57; 73,86</t>
+          <t>66,17; 73,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,07; 80,6</t>
+          <t>72,7; 80,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>74,57; 80,67</t>
+          <t>74,95; 81,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75,37; 80,52</t>
+          <t>75,21; 80,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,01; 79,45</t>
+          <t>73,86; 79,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,11; 85,1</t>
+          <t>80,24; 85,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,46; 83,39</t>
+          <t>78,56; 83,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,12; 87,59</t>
+          <t>80,15; 88,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,2; 86,17</t>
+          <t>77,44; 86,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,96; 86,96</t>
+          <t>79,47; 87,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,92; 80,59</t>
+          <t>72,15; 80,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,99; 74,58</t>
+          <t>64,96; 74,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,06; 78,75</t>
+          <t>69,24; 79,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,95; 83,5</t>
+          <t>74,75; 83,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,25; 74,85</t>
+          <t>67,15; 74,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73,77; 79,81</t>
+          <t>73,65; 80,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74,79; 81,36</t>
+          <t>74,49; 81,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78,14; 84,12</t>
+          <t>77,97; 84,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,74; 76,69</t>
+          <t>71,07; 76,71</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,22; 90,23</t>
+          <t>83,29; 90,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,83; 84,95</t>
+          <t>76,99; 85,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,09; 85,16</t>
+          <t>77,18; 86,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,95; 83,08</t>
+          <t>74,83; 84,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,6; 77,08</t>
+          <t>68,24; 77,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,42; 70,55</t>
+          <t>61,47; 70,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,36; 72,14</t>
+          <t>62,59; 72,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,0; 74,56</t>
+          <t>66,67; 74,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,99; 82,81</t>
+          <t>77,07; 83,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,36; 76,88</t>
+          <t>70,61; 77,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,11; 78,06</t>
+          <t>71,04; 77,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,3; 76,34</t>
+          <t>71,65; 78,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,45; 80,58</t>
+          <t>68,08; 80,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76,16; 86,82</t>
+          <t>75,69; 86,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,68; 88,33</t>
+          <t>79,41; 88,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,19; 89,82</t>
+          <t>83,05; 90,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,19; 67,79</t>
+          <t>54,57; 67,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,09; 74,93</t>
+          <t>62,07; 74,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,92; 78,38</t>
+          <t>66,35; 78,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,22; 80,66</t>
+          <t>74,79; 81,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63,61; 72,56</t>
+          <t>63,02; 72,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70,54; 78,8</t>
+          <t>70,38; 78,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74,09; 81,83</t>
+          <t>74,1; 82,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,46; 83,94</t>
+          <t>79,93; 84,9</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80,72; 89,37</t>
+          <t>81,11; 89,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,76; 85,91</t>
+          <t>76,2; 85,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,58; 84,36</t>
+          <t>75,22; 84,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72,85; 81,09</t>
+          <t>73,68; 81,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,79; 70,06</t>
+          <t>59,18; 70,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,32; 77,73</t>
+          <t>67,67; 78,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,88; 76,7</t>
+          <t>65,73; 76,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61,92; 70,53</t>
+          <t>61,88; 70,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71,29; 78,43</t>
+          <t>71,35; 78,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73,77; 80,77</t>
+          <t>73,48; 80,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72,24; 79,33</t>
+          <t>71,46; 79,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68,87; 75,02</t>
+          <t>69,14; 74,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,86; 88,4</t>
+          <t>82,78; 88,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81,04; 87,1</t>
+          <t>80,96; 87,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,35; 87,07</t>
+          <t>81,09; 87,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,37; 86,48</t>
+          <t>80,84; 86,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,04; 75,17</t>
+          <t>67,82; 75,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,16; 78,8</t>
+          <t>72,02; 78,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,14; 77,13</t>
+          <t>70,37; 77,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,68; 90,64</t>
+          <t>70,3; 76,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76,43; 80,89</t>
+          <t>76,45; 80,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77,18; 81,85</t>
+          <t>77,12; 81,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76,79; 81,33</t>
+          <t>76,78; 81,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,73; 87,94</t>
+          <t>76,32; 80,49</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>79,72; 85,23</t>
+          <t>79,18; 85,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,62; 87,87</t>
+          <t>82,45; 87,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,23; 88,9</t>
+          <t>83,88; 88,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,18; 93,42</t>
+          <t>78,89; 83,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>70,31; 76,68</t>
+          <t>70,39; 76,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,41; 83,93</t>
+          <t>78,34; 83,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,63; 83,56</t>
+          <t>77,82; 83,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>68,16; 73,69</t>
+          <t>69,04; 74,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75,83; 80,21</t>
+          <t>75,58; 80,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81,36; 85,18</t>
+          <t>81,2; 85,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81,55; 85,38</t>
+          <t>81,6; 85,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>75,21; 87,6</t>
+          <t>74,76; 78,39</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>82,67; 85,29</t>
+          <t>82,78; 85,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>81,61; 84,39</t>
+          <t>81,59; 84,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82,69; 85,25</t>
+          <t>82,6; 85,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,16; 85,94</t>
+          <t>79,98; 82,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69,85; 73,07</t>
+          <t>69,81; 72,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,53; 74,64</t>
+          <t>71,51; 74,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,22; 76,33</t>
+          <t>73,2; 76,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>68,71; 77,11</t>
+          <t>71,19; 73,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>76,63; 78,6</t>
+          <t>76,59; 78,7</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76,96; 78,95</t>
+          <t>76,91; 79,11</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78,41; 80,23</t>
+          <t>78,26; 80,32</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>74,83; 80,02</t>
+          <t>75,89; 77,65</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233743</t>
+          <t>239505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>192708</t>
+          <t>212010</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>426449</t>
+          <t>451515</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>214739; 238639</t>
+          <t>214870; 239915</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>211545; 239705</t>
+          <t>211353; 239532</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>202000; 231491</t>
+          <t>202950; 232967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>216895; 248161</t>
+          <t>225020; 255528</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>192321; 219266</t>
+          <t>191516; 219012</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>152219; 189878</t>
+          <t>154370; 187960</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>171910; 205912</t>
+          <t>173946; 207576</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>177248; 205790</t>
+          <t>198007; 224270</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>417368; 451888</t>
+          <t>416987; 453486</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>374497; 420290</t>
+          <t>376110; 420486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>386489; 429956</t>
+          <t>384867; 430007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>401245; 448633</t>
+          <t>430826; 469685</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434999</t>
+          <t>445660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>401055</t>
+          <t>425808</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>836054</t>
+          <t>871468</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>400176; 432187</t>
+          <t>401930; 434436</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>401755; 437213</t>
+          <t>403394; 438271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>426419; 455891</t>
+          <t>425379; 455920</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>412083; 452011</t>
+          <t>424175; 464259</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>339956; 378437</t>
+          <t>339325; 379575</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>342792; 386090</t>
+          <t>345893; 385020</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>380711; 419957</t>
+          <t>378778; 421915</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>384026; 415430</t>
+          <t>409584; 442917</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>751412; 802770</t>
+          <t>749843; 803005</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>758130; 813936</t>
+          <t>756674; 813136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>819086; 870097</t>
+          <t>820448; 871770</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>810808; 861706</t>
+          <t>846248; 895730</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>242506</t>
+          <t>242710</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>248518</t>
+          <t>253635</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>491023</t>
+          <t>496346</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>252261; 279270</t>
+          <t>255543; 281110</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>248724; 277618</t>
+          <t>249497; 278136</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>248643; 273842</t>
+          <t>250238; 274431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227294; 254708</t>
+          <t>228005; 254540</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>217969; 250141</t>
+          <t>217867; 250134</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>235508; 268543</t>
+          <t>236132; 269456</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>245343; 277024</t>
+          <t>247995; 277919</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>234796; 261319</t>
+          <t>239301; 266941</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>482628; 522155</t>
+          <t>481838; 523974</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>496029; 539609</t>
+          <t>494029; 537422</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>505302; 543965</t>
+          <t>504184; 543347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>470535; 510150</t>
+          <t>477849; 515761</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>244564</t>
+          <t>299163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>295078</t>
+          <t>300133</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>539641</t>
+          <t>599297</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>297672; 322741</t>
+          <t>297894; 323098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>282790; 312660</t>
+          <t>283362; 314665</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>283779; 313515</t>
+          <t>284120; 317148</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>228021; 259675</t>
+          <t>279227; 315422</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>254805; 286311</t>
+          <t>253472; 288239</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>238350; 273797</t>
+          <t>238552; 275153</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>240324; 278012</t>
+          <t>241206; 280333</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>180769; 354700</t>
+          <t>281313; 316330</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>561338; 603759</t>
+          <t>561958; 605373</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>532049; 581284</t>
+          <t>533930; 582385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>535830; 588222</t>
+          <t>535280; 584744</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>396522; 601759</t>
+          <t>569723; 621897</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154425</t>
+          <t>179173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>160370</t>
+          <t>177677</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>314795</t>
+          <t>356849</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>138555; 163106</t>
+          <t>137806; 163559</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>161136; 183699</t>
+          <t>160156; 183765</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162453; 182375</t>
+          <t>163965; 183671</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146906; 160543</t>
+          <t>170815; 186159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>112535; 140768</t>
+          <t>113316; 140858</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>135780; 163864</t>
+          <t>135752; 162559</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>142381; 169315</t>
+          <t>143319; 169620</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>152490; 167988</t>
+          <t>169634; 185032</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>260875; 297548</t>
+          <t>258435; 298272</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>303542; 339056</t>
+          <t>302816; 338549</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>313007; 345709</t>
+          <t>313076; 347082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>303661; 324864</t>
+          <t>345688; 367170</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208664</t>
+          <t>210722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>170746</t>
+          <t>175600</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>379409</t>
+          <t>386322</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>218602; 242016</t>
+          <t>219667; 241779</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>206017; 233635</t>
+          <t>207230; 233771</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>195509; 221153</t>
+          <t>197184; 222494</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196436; 218638</t>
+          <t>199455; 220729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>163520; 194872</t>
+          <t>164595; 195908</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>187816; 216844</t>
+          <t>188769; 218758</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>179937; 209473</t>
+          <t>179509; 209369</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>159163; 181295</t>
+          <t>163207; 186971</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>391339; 430522</t>
+          <t>391658; 431243</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>406419; 444963</t>
+          <t>404800; 445534</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>386658; 424622</t>
+          <t>382518; 424941</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>362754; 395111</t>
+          <t>369526; 400784</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>522660</t>
+          <t>604716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>679804</t>
+          <t>565658</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1202464</t>
+          <t>1170375</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>508821; 542842</t>
+          <t>508325; 544154</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>528459; 567988</t>
+          <t>527986; 567955</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>531336; 568655</t>
+          <t>529597; 570129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>501712; 539859</t>
+          <t>581782; 623868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>433001; 478431</t>
+          <t>431621; 477952</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>497961; 543775</t>
+          <t>496944; 542169</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>478792; 526543</t>
+          <t>480361; 528465</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>617284; 769790</t>
+          <t>542753; 588091</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>955789; 1011600</t>
+          <t>956069; 1011086</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1035949; 1098557</t>
+          <t>1035075; 1099713</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1025778; 1086353</t>
+          <t>1025646; 1085823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1145389; 1295789</t>
+          <t>1138447; 1200707</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>798993</t>
+          <t>652585</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>509857</t>
+          <t>595727</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1308850</t>
+          <t>1248312</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>592986; 633934</t>
+          <t>588915; 632258</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>631337; 671460</t>
+          <t>630055; 671741</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>654211; 690455</t>
+          <t>651515; 691157</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>744656; 867590</t>
+          <t>629579; 669538</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>550868; 600788</t>
+          <t>551518; 601987</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>636166; 681009</t>
+          <t>635617; 681117</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>633234; 681556</t>
+          <t>634744; 682657</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>489172; 528861</t>
+          <t>573913; 616572</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1158217; 1225106</t>
+          <t>1154330; 1221857</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1281817; 1341967</t>
+          <t>1279384; 1340199</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1298501; 1359617</t>
+          <t>1299335; 1359418</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1238232; 1442297</t>
+          <t>1218088; 1277304</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2840552</t>
+          <t>2874234</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2658133</t>
+          <t>2706250</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5498686</t>
+          <t>5580484</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2706368; 2792019</t>
+          <t>2710132; 2790716</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2760419; 2854379</t>
+          <t>2759784; 2856332</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2789225; 2875766</t>
+          <t>2786301; 2877168</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2773520; 2973323</t>
+          <t>2825560; 2918160</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2359049; 2467710</t>
+          <t>2357868; 2465095</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2528669; 2638493</t>
+          <t>2528033; 2634771</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2573184; 2682369</t>
+          <t>2572527; 2680009</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2515853; 2823690</t>
+          <t>2658907; 2753058</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5096678; 5227843</t>
+          <t>5094118; 5234445</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5323512; 5461653</t>
+          <t>5320468; 5472520</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5400612; 5525809</t>
+          <t>5390043; 5532141</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5329362; 5698928</t>
+          <t>5515307; 5643081</t>
         </is>
       </c>
     </row>
